--- a/Data/Metdata2.xlsx
+++ b/Data/Metdata2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felix\Downloads\SOAPI1and2-MicrobesAndSurfactants\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A509D8B-B41C-4650-A9B6-F7357691EC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9389394F-7AF5-47E6-ADC9-F544090C5751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="115">
   <si>
     <t>sample</t>
   </si>
@@ -65,15 +65,6 @@
   </si>
   <si>
     <t>POSMV.Longitude</t>
-  </si>
-  <si>
-    <t>Relative.Wind.Speed.1</t>
-  </si>
-  <si>
-    <t>Sea.Surface.Temperature</t>
-  </si>
-  <si>
-    <t>Sea.Surface.Salinity</t>
   </si>
   <si>
     <t>An_612 nm</t>
@@ -755,14 +746,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -797,10 +788,10 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="N1" t="s">
         <v>11</v>
@@ -814,67 +805,58 @@
       <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" t="s">
-        <v>16</v>
-      </c>
       <c r="T1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
+      </c>
+      <c r="U1" t="s">
+        <v>111</v>
       </c>
       <c r="V1" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="W1" t="s">
         <v>113</v>
       </c>
-      <c r="X1" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" t="s">
         <v>59</v>
       </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L2">
         <v>1.210375724705828</v>
@@ -895,66 +877,57 @@
         <v>74.746051311148094</v>
       </c>
       <c r="R2">
-        <v>4.7567387687188001</v>
+        <v>0.367946</v>
       </c>
       <c r="S2">
-        <v>24.134269550748801</v>
+        <v>0.14892188319999999</v>
       </c>
       <c r="T2">
-        <v>32.066367054908497</v>
+        <v>1.0177813360000001</v>
       </c>
       <c r="U2">
-        <v>0.367946</v>
+        <v>0.93461323799999996</v>
       </c>
       <c r="V2">
-        <v>0.14892188319999999</v>
+        <v>0.99394262499999997</v>
       </c>
       <c r="W2">
-        <v>1.0177813360000001</v>
-      </c>
-      <c r="X2">
-        <v>0.93461323799999996</v>
-      </c>
-      <c r="Y2">
-        <v>0.99394262499999997</v>
-      </c>
-      <c r="Z2">
         <v>1.0135162179999999</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" t="s">
         <v>63</v>
       </c>
-      <c r="G3" t="s">
-        <v>66</v>
-      </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L3">
         <v>1.71979530014182</v>
@@ -975,66 +948,57 @@
         <v>74.741217630849206</v>
       </c>
       <c r="R3">
-        <v>8.3080279232111707</v>
+        <v>0.387818</v>
       </c>
       <c r="S3">
-        <v>24.9513339688042</v>
+        <v>4.880692314E-2</v>
       </c>
       <c r="T3">
-        <v>32.512943154246102</v>
+        <v>1.0397714280000001</v>
       </c>
       <c r="U3">
-        <v>0.387818</v>
+        <v>0.91694780499999995</v>
       </c>
       <c r="V3">
-        <v>4.880692314E-2</v>
+        <v>0.71467997900000002</v>
       </c>
       <c r="W3">
-        <v>1.0397714280000001</v>
-      </c>
-      <c r="X3">
-        <v>0.91694780499999995</v>
-      </c>
-      <c r="Y3">
-        <v>0.71467997900000002</v>
-      </c>
-      <c r="Z3">
         <v>1.712227709</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" t="s">
         <v>64</v>
-      </c>
-      <c r="G4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" t="s">
-        <v>67</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
       <c r="J4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" t="s">
         <v>73</v>
-      </c>
-      <c r="K4" t="s">
-        <v>76</v>
       </c>
       <c r="L4">
         <v>1.4628838574439298</v>
@@ -1055,66 +1019,57 @@
         <v>74.753836154899901</v>
       </c>
       <c r="R4">
-        <v>5.9657505285412302</v>
+        <v>0.37828099999999998</v>
       </c>
       <c r="S4">
-        <v>24.364775974710199</v>
+        <v>0.16690298240000001</v>
       </c>
       <c r="T4">
-        <v>32.394362065331897</v>
+        <v>1.1079299650000001</v>
       </c>
       <c r="U4">
-        <v>0.37828099999999998</v>
+        <v>0.998397215</v>
       </c>
       <c r="V4">
-        <v>0.16690298240000001</v>
+        <v>0.82067216300000001</v>
       </c>
       <c r="W4">
-        <v>1.1079299650000001</v>
-      </c>
-      <c r="X4">
-        <v>0.998397215</v>
-      </c>
-      <c r="Y4">
-        <v>0.82067216300000001</v>
-      </c>
-      <c r="Z4">
         <v>0.86245655700000001</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L5">
         <v>1.3254858166860806</v>
@@ -1135,66 +1090,57 @@
         <v>74.756259061757703</v>
       </c>
       <c r="R5">
-        <v>1.51377672209026</v>
+        <v>0.37590499999999999</v>
       </c>
       <c r="S5">
-        <v>23.706284560570101</v>
+        <v>3.9307459279999998E-2</v>
       </c>
       <c r="T5">
-        <v>32.515353206650801</v>
+        <v>0.120676174</v>
       </c>
       <c r="U5">
-        <v>0.37590499999999999</v>
+        <v>1.251840485</v>
       </c>
       <c r="V5">
-        <v>3.9307459279999998E-2</v>
+        <v>1.216950352</v>
       </c>
       <c r="W5">
-        <v>0.120676174</v>
-      </c>
-      <c r="X5">
-        <v>1.251840485</v>
-      </c>
-      <c r="Y5">
-        <v>1.216950352</v>
-      </c>
-      <c r="Z5">
         <v>1.1208633750000001</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
         <v>60</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>63</v>
       </c>
-      <c r="G6" t="s">
-        <v>66</v>
-      </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L6">
         <v>1.2254355986437719</v>
@@ -1215,66 +1161,57 @@
         <v>74.7674473039514</v>
       </c>
       <c r="R6">
-        <v>12.5306990881459</v>
+        <v>0.35928300000000002</v>
       </c>
       <c r="S6">
-        <v>25.3412797583082</v>
+        <v>5.7359310750000003E-2</v>
       </c>
       <c r="T6">
-        <v>32.5085558912387</v>
+        <v>0.22045880600000001</v>
       </c>
       <c r="U6">
-        <v>0.35928300000000002</v>
+        <v>1.2768678950000001</v>
       </c>
       <c r="V6">
-        <v>5.7359310750000003E-2</v>
+        <v>1.1500496840000001</v>
       </c>
       <c r="W6">
-        <v>0.22045880600000001</v>
-      </c>
-      <c r="X6">
-        <v>1.2768678950000001</v>
-      </c>
-      <c r="Y6">
-        <v>1.1500496840000001</v>
-      </c>
-      <c r="Z6">
         <v>1.045528499</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I7">
         <v>6</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L7">
         <v>1.4260659089248082</v>
@@ -1295,66 +1232,57 @@
         <v>74.744271989298497</v>
       </c>
       <c r="R7">
-        <v>10.436407185628701</v>
+        <v>0.34326099999999998</v>
       </c>
       <c r="S7">
-        <v>24.753354815695602</v>
+        <v>0.17333692085000002</v>
       </c>
       <c r="T7">
-        <v>32.4790557669441</v>
+        <v>0.84146813399999998</v>
       </c>
       <c r="U7">
-        <v>0.34326099999999998</v>
+        <v>1.1760448219999999</v>
       </c>
       <c r="V7">
-        <v>0.17333692085000002</v>
+        <v>0.90158522699999999</v>
       </c>
       <c r="W7">
-        <v>0.84146813399999998</v>
-      </c>
-      <c r="X7">
-        <v>1.1760448219999999</v>
-      </c>
-      <c r="Y7">
-        <v>0.90158522699999999</v>
-      </c>
-      <c r="Z7">
         <v>0.77144548199999996</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
         <v>53</v>
-      </c>
-      <c r="C8" t="s">
-        <v>56</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" t="s">
         <v>64</v>
-      </c>
-      <c r="G8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" t="s">
-        <v>67</v>
       </c>
       <c r="I8">
         <v>7</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L8">
         <v>2.0210629364598041</v>
@@ -1375,66 +1303,57 @@
         <v>73.734268660732994</v>
       </c>
       <c r="R8">
-        <v>4.4303664921466002</v>
+        <v>0.35123900000000002</v>
       </c>
       <c r="S8">
-        <v>26.589440209424101</v>
+        <v>0.12760020259999999</v>
       </c>
       <c r="T8">
-        <v>32.876867434555002</v>
+        <v>0.95493317899999997</v>
       </c>
       <c r="U8">
-        <v>0.35123900000000002</v>
+        <v>1.1261249170000001</v>
       </c>
       <c r="V8">
-        <v>0.12760020259999999</v>
+        <v>0.70600487999999995</v>
       </c>
       <c r="W8">
-        <v>0.95493317899999997</v>
-      </c>
-      <c r="X8">
-        <v>1.1261249170000001</v>
-      </c>
-      <c r="Y8">
-        <v>0.70600487999999995</v>
-      </c>
-      <c r="Z8">
         <v>1.126069083</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
         <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>56</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
         <v>59</v>
       </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I9">
         <v>8</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N9">
         <v>3749.7331507890999</v>
@@ -1448,64 +1367,55 @@
       <c r="Q9">
         <v>73.726927259684402</v>
       </c>
-      <c r="R9">
-        <v>1.8596843615495</v>
-      </c>
       <c r="S9">
-        <v>27.087228550932601</v>
+        <v>0.18364502469999999</v>
       </c>
       <c r="T9">
-        <v>33.522622238163599</v>
+        <v>1.20053411</v>
+      </c>
+      <c r="U9">
+        <v>0.58215878200000004</v>
       </c>
       <c r="V9">
-        <v>0.18364502469999999</v>
+        <v>0.28072658299999997</v>
       </c>
       <c r="W9">
-        <v>1.20053411</v>
-      </c>
-      <c r="X9">
-        <v>0.58215878200000004</v>
-      </c>
-      <c r="Y9">
-        <v>0.28072658299999997</v>
-      </c>
-      <c r="Z9">
         <v>2.401537909</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I10">
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L10">
         <v>1.6476419431026168</v>
@@ -1526,66 +1436,57 @@
         <v>75.420849906687394</v>
       </c>
       <c r="R10">
-        <v>10.9869362363919</v>
+        <v>3.4566870000000001</v>
       </c>
       <c r="S10">
-        <v>24.482367962674999</v>
+        <v>1.9699271550000001E-2</v>
       </c>
       <c r="T10">
-        <v>32.551018506998403</v>
+        <v>0.373564018</v>
       </c>
       <c r="U10">
-        <v>3.4566870000000001</v>
+        <v>1.1671617320000001</v>
       </c>
       <c r="V10">
-        <v>1.9699271550000001E-2</v>
+        <v>1.3291716609999999</v>
       </c>
       <c r="W10">
-        <v>0.373564018</v>
-      </c>
-      <c r="X10">
-        <v>1.1671617320000001</v>
-      </c>
-      <c r="Y10">
-        <v>1.3291716609999999</v>
-      </c>
-      <c r="Z10">
         <v>0.60212999599999995</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
         <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I11">
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L11">
         <v>1.274422191164976</v>
@@ -1606,66 +1507,57 @@
         <v>73.729440882893201</v>
       </c>
       <c r="R11">
-        <v>11.7749712973594</v>
+        <v>0.14643600000000001</v>
       </c>
       <c r="S11">
-        <v>26.050612743972401</v>
+        <v>6.2685142789999995E-2</v>
       </c>
       <c r="T11">
-        <v>33.353279678530399</v>
+        <v>0.95433047199999999</v>
       </c>
       <c r="U11">
-        <v>0.14643600000000001</v>
+        <v>1.059808718</v>
       </c>
       <c r="V11">
-        <v>6.2685142789999995E-2</v>
+        <v>0.85044775699999997</v>
       </c>
       <c r="W11">
-        <v>0.95433047199999999</v>
-      </c>
-      <c r="X11">
-        <v>1.059808718</v>
-      </c>
-      <c r="Y11">
-        <v>0.85044775699999997</v>
-      </c>
-      <c r="Z11">
         <v>1.15410301</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
         <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I12">
         <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L12">
         <v>1.4352140853821467</v>
@@ -1686,66 +1578,57 @@
         <v>73.723339608899295</v>
       </c>
       <c r="R12">
-        <v>7.3740046838407496</v>
+        <v>0.21935499999999999</v>
       </c>
       <c r="S12">
-        <v>26.383348946135801</v>
+        <v>3.0722719669999999E-2</v>
       </c>
       <c r="T12">
-        <v>33.221428337236503</v>
+        <v>0.73685869800000003</v>
       </c>
       <c r="U12">
-        <v>0.21935499999999999</v>
+        <v>1.113223933</v>
       </c>
       <c r="V12">
-        <v>3.0722719669999999E-2</v>
+        <v>0.87584164399999997</v>
       </c>
       <c r="W12">
-        <v>0.73685869800000003</v>
-      </c>
-      <c r="X12">
-        <v>1.113223933</v>
-      </c>
-      <c r="Y12">
-        <v>0.87584164399999997</v>
-      </c>
-      <c r="Z12">
         <v>1.494168317</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
         <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>56</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
         <v>61</v>
       </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I13">
         <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L13">
         <v>1.0319668981463914</v>
@@ -1766,66 +1649,57 @@
         <v>73.724618743662006</v>
       </c>
       <c r="R13">
-        <v>9.2776685393258393</v>
+        <v>0.22037100000000001</v>
       </c>
       <c r="S13">
-        <v>26.1300728033473</v>
+        <v>0.2015244293</v>
       </c>
       <c r="T13">
-        <v>33.148551743375201</v>
+        <v>1.141708548</v>
       </c>
       <c r="U13">
-        <v>0.22037100000000001</v>
+        <v>0.891292109</v>
       </c>
       <c r="V13">
-        <v>0.2015244293</v>
+        <v>0.72474340400000004</v>
       </c>
       <c r="W13">
-        <v>1.141708548</v>
-      </c>
-      <c r="X13">
-        <v>0.891292109</v>
-      </c>
-      <c r="Y13">
-        <v>0.72474340400000004</v>
-      </c>
-      <c r="Z13">
         <v>1.431708137</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" t="s">
         <v>59</v>
       </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
       <c r="G14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" t="s">
         <v>66</v>
-      </c>
-      <c r="H14" t="s">
-        <v>69</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L14">
         <v>1.3423412222453295</v>
@@ -1846,66 +1720,57 @@
         <v>74.757480857142895</v>
       </c>
       <c r="R14">
-        <v>5.2285714285714304</v>
+        <v>0.321633</v>
       </c>
       <c r="S14">
-        <v>23.5725571428571</v>
+        <v>3.5614215890000002E-2</v>
       </c>
       <c r="T14">
-        <v>32.119285714285702</v>
+        <v>0.33211333300000001</v>
       </c>
       <c r="U14">
-        <v>0.321633</v>
+        <v>1.111765766</v>
       </c>
       <c r="V14">
-        <v>3.5614215890000002E-2</v>
+        <v>1.395355694</v>
       </c>
       <c r="W14">
-        <v>0.33211333300000001</v>
-      </c>
-      <c r="X14">
-        <v>1.111765766</v>
-      </c>
-      <c r="Y14">
-        <v>1.395355694</v>
-      </c>
-      <c r="Z14">
         <v>0.58033592099999998</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" t="s">
         <v>63</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>66</v>
-      </c>
-      <c r="H15" t="s">
-        <v>69</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
       <c r="J15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L15">
         <v>2.0970031532051885</v>
@@ -1926,66 +1791,57 @@
         <v>74.729549857142899</v>
       </c>
       <c r="R15">
-        <v>7.7285714285714304</v>
-      </c>
-      <c r="S15">
-        <v>24.869314285714299</v>
+        <v>0.376</v>
+      </c>
+      <c r="S15" t="e">
+        <v>#N/A</v>
       </c>
       <c r="T15">
-        <v>32.5126285714286</v>
+        <v>0.35504083199999997</v>
       </c>
       <c r="U15">
-        <v>0.376</v>
-      </c>
-      <c r="V15" t="e">
-        <v>#N/A</v>
+        <v>1.0605394880000001</v>
+      </c>
+      <c r="V15">
+        <v>1.4381861920000001</v>
       </c>
       <c r="W15">
-        <v>0.35504083199999997</v>
-      </c>
-      <c r="X15">
-        <v>1.0605394880000001</v>
-      </c>
-      <c r="Y15">
-        <v>1.4381861920000001</v>
-      </c>
-      <c r="Z15">
         <v>0.85938648500000003</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" t="s">
         <v>66</v>
-      </c>
-      <c r="H16" t="s">
-        <v>69</v>
       </c>
       <c r="I16">
         <v>3</v>
       </c>
       <c r="J16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N16">
         <v>3843.0949428571398</v>
@@ -2000,66 +1856,57 @@
         <v>74.748271714285707</v>
       </c>
       <c r="R16">
-        <v>6.6142857142857103</v>
+        <v>0.3569</v>
       </c>
       <c r="S16">
-        <v>24.518171428571399</v>
+        <v>8.8525318059999997E-2</v>
       </c>
       <c r="T16">
-        <v>32.416714285714299</v>
+        <v>0.54819545400000003</v>
       </c>
       <c r="U16">
-        <v>0.3569</v>
+        <v>0.82534116099999999</v>
       </c>
       <c r="V16">
-        <v>8.8525318059999997E-2</v>
+        <v>1.616358365</v>
       </c>
       <c r="W16">
-        <v>0.54819545400000003</v>
-      </c>
-      <c r="X16">
-        <v>0.82534116099999999</v>
-      </c>
-      <c r="Y16">
-        <v>1.616358365</v>
-      </c>
-      <c r="Z16">
         <v>0.88490183</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I17">
         <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L17">
         <v>1.2752719502372916</v>
@@ -2080,66 +1927,57 @@
         <v>74.752873571428594</v>
       </c>
       <c r="R17">
-        <v>3.9142857142857101</v>
+        <v>0.34646700000000002</v>
       </c>
       <c r="S17">
-        <v>23.370742857142901</v>
+        <v>1.9596373779999999E-2</v>
       </c>
       <c r="T17">
-        <v>32.513585714285703</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>0.34646700000000002</v>
+        <v>1.2545878699999999</v>
       </c>
       <c r="V17">
-        <v>1.9596373779999999E-2</v>
+        <v>1.3022935959999999</v>
       </c>
       <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>1.2545878699999999</v>
-      </c>
-      <c r="Y17">
-        <v>1.3022935959999999</v>
-      </c>
-      <c r="Z17">
         <v>0.659695272</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" t="s">
         <v>60</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>63</v>
       </c>
-      <c r="G18" t="s">
-        <v>66</v>
-      </c>
       <c r="H18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I18">
         <v>5</v>
       </c>
       <c r="J18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L18">
         <v>1.1811989613317737</v>
@@ -2160,66 +1998,57 @@
         <v>74.753464857142902</v>
       </c>
       <c r="R18">
-        <v>15.757142857142901</v>
-      </c>
-      <c r="S18">
-        <v>25.349814285714299</v>
+        <v>0.366033</v>
+      </c>
+      <c r="S18" t="e">
+        <v>#N/A</v>
       </c>
       <c r="T18">
-        <v>32.503828571428599</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>0.366033</v>
-      </c>
-      <c r="V18" t="e">
-        <v>#N/A</v>
+        <v>1.1656926649999999</v>
+      </c>
+      <c r="V18">
+        <v>1.379130084</v>
       </c>
       <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>1.1656926649999999</v>
-      </c>
-      <c r="Y18">
-        <v>1.379130084</v>
-      </c>
-      <c r="Z18">
         <v>0.83241847300000005</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I19">
         <v>6</v>
       </c>
       <c r="J19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L19">
         <v>1.1882252325598956</v>
@@ -2240,66 +2069,57 @@
         <v>74.743995142857102</v>
       </c>
       <c r="R19">
-        <v>9.71428571428571</v>
+        <v>0.32093300000000002</v>
       </c>
       <c r="S19">
-        <v>24.8152857142857</v>
+        <v>3.1794716069999999E-2</v>
       </c>
       <c r="T19">
-        <v>32.497799999999998</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>0.32093300000000002</v>
+        <v>1.1770748959999999</v>
       </c>
       <c r="V19">
-        <v>3.1794716069999999E-2</v>
+        <v>1.3730314640000001</v>
       </c>
       <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>1.1770748959999999</v>
-      </c>
-      <c r="Y19">
-        <v>1.3730314640000001</v>
-      </c>
-      <c r="Z19">
         <v>0.83688946600000003</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D20">
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" t="s">
         <v>66</v>
-      </c>
-      <c r="H20" t="s">
-        <v>69</v>
       </c>
       <c r="I20">
         <v>7</v>
       </c>
       <c r="J20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L20">
         <v>1.226904855670707</v>
@@ -2320,66 +2140,57 @@
         <v>73.736214285714297</v>
       </c>
       <c r="R20">
-        <v>4.6714285714285699</v>
-      </c>
-      <c r="S20">
-        <v>26.605257142857099</v>
+        <v>0.35589999999999999</v>
+      </c>
+      <c r="S20" t="e">
+        <v>#N/A</v>
       </c>
       <c r="T20">
-        <v>32.868214285714302</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>0.35589999999999999</v>
-      </c>
-      <c r="V20" t="e">
-        <v>#N/A</v>
+        <v>1.148312765</v>
+      </c>
+      <c r="V20">
+        <v>1.389643709</v>
       </c>
       <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>1.148312765</v>
-      </c>
-      <c r="Y20">
-        <v>1.389643709</v>
-      </c>
-      <c r="Z20">
         <v>0.952800596</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D21">
         <v>2</v>
       </c>
       <c r="E21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" t="s">
         <v>59</v>
       </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
       <c r="G21" t="s">
+        <v>63</v>
+      </c>
+      <c r="H21" t="s">
         <v>66</v>
-      </c>
-      <c r="H21" t="s">
-        <v>69</v>
       </c>
       <c r="I21">
         <v>8</v>
       </c>
       <c r="J21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L21">
         <v>1.1813394867563363</v>
@@ -2400,66 +2211,57 @@
         <v>73.7356508571429</v>
       </c>
       <c r="R21">
-        <v>4.1428571428571397</v>
+        <v>0.36763299999999999</v>
       </c>
       <c r="S21">
-        <v>27.310842857142902</v>
+        <v>4.5529997099999997E-2</v>
       </c>
       <c r="T21">
-        <v>33.578600000000002</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>0.36763299999999999</v>
+        <v>0.91611756700000002</v>
       </c>
       <c r="V21">
-        <v>4.5529997099999997E-2</v>
+        <v>1.6199279559999999</v>
       </c>
       <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0.91611756700000002</v>
-      </c>
-      <c r="Y21">
-        <v>1.6199279559999999</v>
-      </c>
-      <c r="Z21">
         <v>1.035870321</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" t="s">
         <v>54</v>
-      </c>
-      <c r="C22" t="s">
-        <v>57</v>
       </c>
       <c r="D22">
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" t="s">
         <v>66</v>
-      </c>
-      <c r="H22" t="s">
-        <v>69</v>
       </c>
       <c r="I22">
         <v>9</v>
       </c>
       <c r="J22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L22">
         <v>1.5090799081920847</v>
@@ -2480,66 +2282,57 @@
         <v>75.435049714285697</v>
       </c>
       <c r="R22">
-        <v>9.2142857142857206</v>
+        <v>1.511717</v>
       </c>
       <c r="S22">
-        <v>26.246157142857101</v>
+        <v>0.11264086057</v>
       </c>
       <c r="T22">
-        <v>32.483814285714303</v>
+        <v>0.29754450300000002</v>
       </c>
       <c r="U22">
-        <v>1.511717</v>
+        <v>1.13947365</v>
       </c>
       <c r="V22">
-        <v>0.11264086057</v>
+        <v>1.4001255699999999</v>
       </c>
       <c r="W22">
-        <v>0.29754450300000002</v>
-      </c>
-      <c r="X22">
-        <v>1.13947365</v>
-      </c>
-      <c r="Y22">
-        <v>1.4001255699999999</v>
-      </c>
-      <c r="Z22">
         <v>0.57063027700000002</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" t="s">
         <v>54</v>
-      </c>
-      <c r="C23" t="s">
-        <v>57</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" t="s">
         <v>66</v>
-      </c>
-      <c r="H23" t="s">
-        <v>69</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
       <c r="J23" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K23" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L23">
         <v>1.348129113169495</v>
@@ -2560,66 +2353,57 @@
         <v>75.413005142857102</v>
       </c>
       <c r="R23">
-        <v>16.328571428571401</v>
+        <v>4.1130000000000004</v>
       </c>
       <c r="S23">
-        <v>25.621085714285702</v>
+        <v>4.8879560840000003E-2</v>
       </c>
       <c r="T23">
-        <v>32.555142857142897</v>
+        <v>0.43572667300000001</v>
       </c>
       <c r="U23">
-        <v>4.1130000000000004</v>
+        <v>1.145635274</v>
       </c>
       <c r="V23">
-        <v>4.8879560840000003E-2</v>
+        <v>1.330318171</v>
       </c>
       <c r="W23">
-        <v>0.43572667300000001</v>
-      </c>
-      <c r="X23">
-        <v>1.145635274</v>
-      </c>
-      <c r="Y23">
-        <v>1.330318171</v>
-      </c>
-      <c r="Z23">
         <v>0.573364557</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I24">
         <v>11</v>
       </c>
       <c r="J24" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L24">
         <v>1.069959035248147</v>
@@ -2640,66 +2424,57 @@
         <v>73.731638857142897</v>
       </c>
       <c r="R24">
-        <v>12.657142857142899</v>
+        <v>0.16273299999999999</v>
       </c>
       <c r="S24">
-        <v>26.022642857142898</v>
+        <v>4.2787771500000002E-2</v>
       </c>
       <c r="T24">
-        <v>33.295714285714297</v>
+        <v>0.41671548600000002</v>
       </c>
       <c r="U24">
-        <v>0.16273299999999999</v>
+        <v>1.1452834030000001</v>
       </c>
       <c r="V24">
-        <v>4.2787771500000002E-2</v>
+        <v>1.2039526060000001</v>
       </c>
       <c r="W24">
-        <v>0.41671548600000002</v>
-      </c>
-      <c r="X24">
-        <v>1.1452834030000001</v>
-      </c>
-      <c r="Y24">
-        <v>1.2039526060000001</v>
-      </c>
-      <c r="Z24">
         <v>1.214472354</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G25" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I25">
         <v>12</v>
       </c>
       <c r="J25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L25">
         <v>1.1381806157375971</v>
@@ -2720,66 +2495,57 @@
         <v>73.715561285714301</v>
       </c>
       <c r="R25">
-        <v>7.7714285714285696</v>
+        <v>0.21953300000000001</v>
       </c>
       <c r="S25">
-        <v>26.414971428571398</v>
+        <v>2.7541136420000001E-2</v>
       </c>
       <c r="T25">
-        <v>33.270514285714299</v>
+        <v>0.31935613000000002</v>
       </c>
       <c r="U25">
-        <v>0.21953300000000001</v>
+        <v>1.149450152</v>
       </c>
       <c r="V25">
-        <v>2.7541136420000001E-2</v>
+        <v>1.236740452</v>
       </c>
       <c r="W25">
-        <v>0.31935613000000002</v>
-      </c>
-      <c r="X25">
-        <v>1.149450152</v>
-      </c>
-      <c r="Y25">
-        <v>1.236740452</v>
-      </c>
-      <c r="Z25">
         <v>1.253339212</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
         <v>53</v>
-      </c>
-      <c r="C26" t="s">
-        <v>56</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I26">
         <v>13</v>
       </c>
       <c r="J26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K26" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L26">
         <v>1.3617628129999999</v>
@@ -2800,66 +2566,57 @@
         <v>73.710162609999998</v>
       </c>
       <c r="R26">
-        <v>8.2095840869999996</v>
+        <v>0.18803300000000001</v>
       </c>
       <c r="S26">
-        <v>26.313958769999999</v>
+        <v>0.15864749</v>
       </c>
       <c r="T26">
-        <v>33.181787159999999</v>
+        <v>0.71760438299999996</v>
       </c>
       <c r="U26">
-        <v>0.18803300000000001</v>
+        <v>1.1246999639999999</v>
       </c>
       <c r="V26">
-        <v>0.15864749</v>
+        <v>0.95620496600000005</v>
       </c>
       <c r="W26">
-        <v>0.71760438299999996</v>
-      </c>
-      <c r="X26">
-        <v>1.1246999639999999</v>
-      </c>
-      <c r="Y26">
-        <v>0.95620496600000005</v>
-      </c>
-      <c r="Z26">
         <v>1.4233662010000001</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="E27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" t="s">
         <v>60</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>63</v>
       </c>
-      <c r="G27" t="s">
-        <v>66</v>
-      </c>
       <c r="H27" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I27">
         <v>13</v>
       </c>
       <c r="J27" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L27">
         <v>1.0906830222354928</v>
@@ -2880,66 +2637,57 @@
         <v>73.698665857142899</v>
       </c>
       <c r="R27">
-        <v>9.1714285714285708</v>
+        <v>0.21356700000000001</v>
       </c>
       <c r="S27">
-        <v>26.179099999999998</v>
+        <v>3.8320408930000001E-2</v>
       </c>
       <c r="T27">
-        <v>33.162057142857101</v>
+        <v>1.125214583</v>
       </c>
       <c r="U27">
-        <v>0.21356700000000001</v>
+        <v>0.92095852899999997</v>
       </c>
       <c r="V27">
-        <v>3.8320408930000001E-2</v>
+        <v>0.79009180899999998</v>
       </c>
       <c r="W27">
-        <v>1.125214583</v>
-      </c>
-      <c r="X27">
-        <v>0.92095852899999997</v>
-      </c>
-      <c r="Y27">
-        <v>0.79009180899999998</v>
-      </c>
-      <c r="Z27">
         <v>1.1908847220000001</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="E28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" t="s">
         <v>61</v>
       </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I28">
         <v>14</v>
       </c>
       <c r="J28" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K28" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L28">
         <v>1.0615766936729973</v>
@@ -2960,66 +2708,57 @@
         <v>73.728304285714302</v>
       </c>
       <c r="R28">
-        <v>8.8428571428571399</v>
+        <v>0.228133</v>
       </c>
       <c r="S28">
-        <v>26.044599999999999</v>
+        <v>8.3367821940000003E-2</v>
       </c>
       <c r="T28">
-        <v>33.099642857142896</v>
+        <v>0.31072738100000002</v>
       </c>
       <c r="U28">
-        <v>0.228133</v>
+        <v>1.2011633070000001</v>
       </c>
       <c r="V28">
-        <v>8.3367821940000003E-2</v>
+        <v>1.1473842139999999</v>
       </c>
       <c r="W28">
-        <v>0.31072738100000002</v>
-      </c>
-      <c r="X28">
-        <v>1.2011633070000001</v>
-      </c>
-      <c r="Y28">
-        <v>1.1473842139999999</v>
-      </c>
-      <c r="Z28">
         <v>1.319708071</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H29" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I29">
         <v>15</v>
       </c>
       <c r="J29" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K29" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L29">
         <v>0.82418360969031235</v>
@@ -3040,66 +2779,57 @@
         <v>74.749896352365397</v>
       </c>
       <c r="R29">
-        <v>6.5796084828711301</v>
+        <v>4.5003909389999999</v>
       </c>
       <c r="S29">
-        <v>17.295412234910302</v>
+        <v>0.107228696</v>
       </c>
       <c r="T29">
-        <v>33.023179445350699</v>
+        <v>1.231577624</v>
       </c>
       <c r="U29">
-        <v>4.5003909389999999</v>
+        <v>0.89533689299999997</v>
       </c>
       <c r="V29">
-        <v>0.107228696</v>
+        <v>0.81449698400000003</v>
       </c>
       <c r="W29">
-        <v>1.231577624</v>
-      </c>
-      <c r="X29">
-        <v>0.89533689299999997</v>
-      </c>
-      <c r="Y29">
-        <v>0.81449698400000003</v>
-      </c>
-      <c r="Z29">
         <v>0.87123016099999995</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" t="s">
         <v>59</v>
       </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
       <c r="G30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I30">
         <v>16</v>
       </c>
       <c r="J30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K30" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L30">
         <v>1.1448588061375549</v>
@@ -3120,66 +2850,57 @@
         <v>74.749496512733401</v>
       </c>
       <c r="R30">
-        <v>9.0803056027164697</v>
+        <v>3.3341481480000001</v>
       </c>
       <c r="S30">
-        <v>19.704673684210501</v>
+        <v>0.144052876</v>
       </c>
       <c r="T30">
-        <v>32.885942954159603</v>
+        <v>1.490642405</v>
       </c>
       <c r="U30">
-        <v>3.3341481480000001</v>
+        <v>0.51040786199999999</v>
       </c>
       <c r="V30">
-        <v>0.144052876</v>
+        <v>0.71445627599999995</v>
       </c>
       <c r="W30">
-        <v>1.490642405</v>
-      </c>
-      <c r="X30">
-        <v>0.51040786199999999</v>
-      </c>
-      <c r="Y30">
-        <v>0.71445627599999995</v>
-      </c>
-      <c r="Z30">
         <v>0.98245093299999997</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F31" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H31" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I31">
         <v>17</v>
       </c>
       <c r="J31" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K31" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L31">
         <v>1.3551570610177461</v>
@@ -3200,66 +2921,57 @@
         <v>74.752147037181999</v>
       </c>
       <c r="R31">
-        <v>12.0632093933464</v>
+        <v>2.0314784879999999</v>
       </c>
       <c r="S31">
-        <v>17.947588454011701</v>
+        <v>0.22957843</v>
       </c>
       <c r="T31">
-        <v>32.854582778865002</v>
+        <v>1.3088262610000001</v>
       </c>
       <c r="U31">
-        <v>2.0314784879999999</v>
+        <v>0.67708197400000003</v>
       </c>
       <c r="V31">
-        <v>0.22957843</v>
+        <v>0.53669816199999998</v>
       </c>
       <c r="W31">
-        <v>1.3088262610000001</v>
-      </c>
-      <c r="X31">
-        <v>0.67708197400000003</v>
-      </c>
-      <c r="Y31">
-        <v>0.53669816199999998</v>
-      </c>
-      <c r="Z31">
         <v>1.872649429</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F32" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" t="s">
         <v>64</v>
-      </c>
-      <c r="G32" t="s">
-        <v>58</v>
-      </c>
-      <c r="H32" t="s">
-        <v>67</v>
       </c>
       <c r="I32">
         <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K32" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>1.2823359456788723</v>
@@ -3280,66 +2992,57 @@
         <v>74.750888490307901</v>
       </c>
       <c r="R32">
-        <v>10.086545039908801</v>
+        <v>1.7267138639999999</v>
       </c>
       <c r="S32">
-        <v>17.020353135689898</v>
+        <v>0.34793330500000003</v>
       </c>
       <c r="T32">
-        <v>33.033850057012501</v>
+        <v>1.3561559919999999</v>
       </c>
       <c r="U32">
-        <v>1.7267138639999999</v>
+        <v>0.82728497099999998</v>
       </c>
       <c r="V32">
-        <v>0.34793330500000003</v>
+        <v>0.67599069000000001</v>
       </c>
       <c r="W32">
-        <v>1.3561559919999999</v>
-      </c>
-      <c r="X32">
-        <v>0.82728497099999998</v>
-      </c>
-      <c r="Y32">
-        <v>0.67599069000000001</v>
-      </c>
-      <c r="Z32">
         <v>0.84907113300000003</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G33" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H33" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I33">
         <v>15</v>
       </c>
       <c r="J33" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K33" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L33">
         <v>0.98326167068259451</v>
@@ -3360,66 +3063,57 @@
         <v>74.757737571428606</v>
       </c>
       <c r="R33">
-        <v>10.714285714285699</v>
-      </c>
-      <c r="S33">
-        <v>17.186728571428599</v>
+        <v>3.619480555</v>
+      </c>
+      <c r="S33" t="e">
+        <v>#N/A</v>
       </c>
       <c r="T33">
-        <v>33.016300000000001</v>
+        <v>0.41357243900000001</v>
       </c>
       <c r="U33">
-        <v>3.619480555</v>
-      </c>
-      <c r="V33" t="e">
-        <v>#N/A</v>
+        <v>1.1966931860000001</v>
+      </c>
+      <c r="V33">
+        <v>1.2316674519999999</v>
       </c>
       <c r="W33">
-        <v>0.41357243900000001</v>
-      </c>
-      <c r="X33">
-        <v>1.1966931860000001</v>
-      </c>
-      <c r="Y33">
-        <v>1.2316674519999999</v>
-      </c>
-      <c r="Z33">
         <v>0.78778494200000004</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" t="s">
         <v>59</v>
       </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H34" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I34">
         <v>16</v>
       </c>
       <c r="J34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K34" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L34">
         <v>1.0426898807580833</v>
@@ -3440,66 +3134,57 @@
         <v>74.749090857142903</v>
       </c>
       <c r="R34">
-        <v>9.9285714285714306</v>
+        <v>2.6021722230000002</v>
       </c>
       <c r="S34">
-        <v>21.846457142857101</v>
+        <v>8.3926487999999994E-2</v>
       </c>
       <c r="T34">
-        <v>32.735785714285697</v>
+        <v>0.41514245999999999</v>
       </c>
       <c r="U34">
-        <v>2.6021722230000002</v>
+        <v>1.1970756629999999</v>
       </c>
       <c r="V34">
-        <v>8.3926487999999994E-2</v>
+        <v>1.2336587429999999</v>
       </c>
       <c r="W34">
-        <v>0.41514245999999999</v>
-      </c>
-      <c r="X34">
-        <v>1.1970756629999999</v>
-      </c>
-      <c r="Y34">
-        <v>1.2336587429999999</v>
-      </c>
-      <c r="Z34">
         <v>0.77694487999999995</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" t="s">
         <v>51</v>
       </c>
-      <c r="B35" t="s">
-        <v>54</v>
-      </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F35" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H35" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I35">
         <v>17</v>
       </c>
       <c r="J35" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K35" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L35">
         <v>1.1411380643172369</v>
@@ -3520,66 +3205,57 @@
         <v>74.7527821428571</v>
       </c>
       <c r="R35">
-        <v>14.842857142857101</v>
+        <v>1.9738333340000001</v>
       </c>
       <c r="S35">
-        <v>20.8098285714286</v>
+        <v>4.4134568999999998E-2</v>
       </c>
       <c r="T35">
-        <v>32.1703571428571</v>
+        <v>0.41872633599999998</v>
       </c>
       <c r="U35">
-        <v>1.9738333340000001</v>
+        <v>1.1921056889999999</v>
       </c>
       <c r="V35">
-        <v>4.4134568999999998E-2</v>
+        <v>1.2279340000000001</v>
       </c>
       <c r="W35">
-        <v>0.41872633599999998</v>
-      </c>
-      <c r="X35">
-        <v>1.1921056889999999</v>
-      </c>
-      <c r="Y35">
-        <v>1.2279340000000001</v>
-      </c>
-      <c r="Z35">
         <v>0.84979509799999997</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F36" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I36">
         <v>18</v>
       </c>
       <c r="J36" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K36" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L36">
         <v>1.0236020714457474</v>
@@ -3600,30 +3276,21 @@
         <v>74.756226571428599</v>
       </c>
       <c r="R36">
-        <v>7.1142857142857103</v>
+        <v>2.1587555549999999</v>
       </c>
       <c r="S36">
-        <v>16.4591142857143</v>
+        <v>6.1584469000000003E-2</v>
       </c>
       <c r="T36">
-        <v>33.012271428571403</v>
+        <v>0.42437574700000003</v>
       </c>
       <c r="U36">
-        <v>2.1587555549999999</v>
+        <v>1.1957816290000001</v>
       </c>
       <c r="V36">
-        <v>6.1584469000000003E-2</v>
+        <v>1.2375328240000001</v>
       </c>
       <c r="W36">
-        <v>0.42437574700000003</v>
-      </c>
-      <c r="X36">
-        <v>1.1957816290000001</v>
-      </c>
-      <c r="Y36">
-        <v>1.2375328240000001</v>
-      </c>
-      <c r="Z36">
         <v>0.74888181099999995</v>
       </c>
     </row>
